--- a/scenarios/S05_ai_expense_automation/deliverables/규정매트릭스_OCR_시트.xlsx
+++ b/scenarios/S05_ai_expense_automation/deliverables/규정매트릭스_OCR_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규정매트릭스" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OCR증빙유형" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테스트케이스" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,4 +869,370 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20260725-여비교통비-규정준수-자동화</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:16:14.366+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>총무 박대리</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S05:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>구축 및 실행은 확정하지 않고, 비용증빙 OCR·multi-hop 규정 검색·위반 판단·신뢰도 및 근거 저장·사람 검토 전환을 요구사항과 검토 대상 파이프라인 범위로 승인한다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>비용증빙 OCR 추출, multi-hop 규정 검색·연결, 위반 판단 및 불확실 건 사람 검토 전환 요구사항 정의</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>기능정의서(여비교통비 자동화); 파이프라인 설계서(OCR·규정 검색·위반 판단); 테스트 시나리오(비용증빙 OCR 및 규정 준수 판단)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/faf870feb7bcc772aa8db8f33fe3c581f5821bf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20260725-여비교통비-규정준수-자동화-승인-실행결과-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:35:22.725+09:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>총무 박대리</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S05:B00001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>기능정의서·파이프라인 설계서·테스트 시나리오를 추가하고 요구사항 추적표·산출물 설계서·보고 장표를 수정한 실행 결과를 승인한다. 실제 구축·운영·자동 승인/반려·비용/회계 연동은 후속 결정 사항으로 남긴다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>여비교통비 OCR·multi-hop 규정 준수 판단 파이프라인의 요구사항 및 검토 범위 반영 완료; 구축·운영과 자동 승인·반려·회계 연동은 후속 결정 필요</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>기능정의서, 파이프라인 설계서, 테스트 시나리오, 요구사항 추적표, 산출물_설계서, 보고_장표</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/fa3f55cca501823f7e4ed7d7f3f0b977e71a9c91</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20260725-여비교통비-규정준수-자동화-승인-실행결과</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:30:26.825+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>총무 박대리</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S05:B00010</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>요구사항 정의, 검토 대상 파이프라인, 기능·설계·테스트·추적 산출물 변경을 승인하며 구축·운영·자동 승인/반려·비용/회계 연동은 후속 결정으로 남긴다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>비용증빙 OCR 추출, 규정·예외 multi-hop 검색, 근거 대조, 위반 판단, 감사 추적, 사람 검토 전환과 관련된 요구사항·설계·테스트·추적 항목을 반영한다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>기능정의서; 파이프라인 설계서; 테스트 시나리오; 요구사항 추적표; 산출물_설계서; 보고_장표</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/06b785e2ee8ae9e0b837c41d1dde49fd5070496b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20260725-여비교통비-규정준수-자동화</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:26:47.593+09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>총무 박대리</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S05:B00100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>요구사항 정의 및 검토 대상 파이프라인 변경을 승인하며, 실제 구축·운영·자동 승인/반려·비용/회계 시스템 연동은 후속 결정 사항으로 남긴다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>비용증빙 OCR, multi-hop 규정·예외 탐색, 근거 대조, 불확실성 사람 검토 전환 및 감사 추적 저장 요구사항 반영</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>기능정의서; 파이프라인 설계서; 테스트 시나리오; 요구사항 추적표; 산출물_설계서; 보고_장표</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/661c8547b17879fa115d056cdbeecda4f7b0e686</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20260725-여비교통비-규정준수-자동화-승인-반영</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:23:34.413+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>총무 박대리</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S05:B01000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>기능정의서·파이프라인 설계서·테스트 시나리오를 추가하고 요구사항 추적표·DOCX·PPTX를 수정하는 범위를 승인한다. 실제 구축·운영, 자동 승인·반려, 비용·회계 시스템 연동은 후속 결정 사항으로 남긴다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>여비교통비 OCR·multi-hop 규정 준수 판단 파이프라인의 요구사항 정의 및 검토 범위를 반영했으며, 구축·자동 승인·회계 연동은 후속 결정 사항입니다.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>기능정의서·파이프라인 설계서·테스트 시나리오 추가 및 요구사항 추적표·DOCX·PPTX 수정</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/ec7ac226d7567ae33a2d99cdb36d4b49c09c8e9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20260725-여비교통비-규정준수-자동화</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:20:05.518+09:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>총무 박대리</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bench:S05:B10000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>요구사항 정의와 검토 대상 파이프라인으로 승인하며, 구축·운영·자동 승인/반려·비용 및 회계 시스템 연동은 후속 결정 사항으로 남긴다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>여비교통비 비용증빙 OCR·multi-hop 규정 준수 판단 파이프라인을 요구사항 및 검토 범위로 정의했으며, 구축·자동 승인/반려는 후속 결정이다.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>기능정의서; 파이프라인 설계서; 테스트 시나리오; 요구사항 추적표</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/456343795e7780782556ad3cfd6cc16b0ad6595a</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>